--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:43</t>
+    <t xml:space="preserve">2026-09-24 01:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -561,7 +561,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.47</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>21</v>
@@ -570,10 +570,10 @@
         <v>-0.11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +593,7 @@
         <v>-0.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>-0.5</v>
@@ -607,7 +607,7 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>21</v>
@@ -616,10 +616,10 @@
         <v>-0.04</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="5">
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>21</v>
@@ -639,7 +639,7 @@
         <v>0.2</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>0.2</v>
@@ -653,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>21</v>
@@ -662,10 +662,10 @@
         <v>0.23</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="7">
@@ -682,13 +682,13 @@
         <v>19</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="8">
@@ -705,13 +705,13 @@
         <v>19</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="9">
@@ -722,19 +722,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.36</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="10">
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>0.08</v>
@@ -768,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>19</v>
@@ -777,7 +777,7 @@
         <v>0.01</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.08</v>
@@ -791,19 +791,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.24</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="13">
@@ -814,16 +814,16 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.39</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>-0.41</v>
@@ -837,19 +837,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.07</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
@@ -860,19 +860,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
     </row>
     <row r="16">
@@ -889,13 +889,13 @@
         <v>19</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="17">
@@ -906,7 +906,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.2</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>19</v>
@@ -915,7 +915,7 @@
         <v>-0.1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>-0.09</v>
@@ -935,13 +935,13 @@
         <v>19</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.41</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="19">
@@ -958,13 +958,13 @@
         <v>19</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="20">
@@ -975,7 +975,7 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>19</v>
@@ -984,10 +984,10 @@
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="21">
@@ -998,19 +998,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>0.52</v>
+        <v>-0.29</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.25</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="22">
@@ -1021,7 +1021,7 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.53</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>21</v>
@@ -1030,10 +1030,10 @@
         <v>-0.06</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="23">
@@ -1044,19 +1044,19 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>21</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.29</v>
+        <v>-0.39</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:33</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_enveje_a_2022_nuble.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
